--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
@@ -244,12 +250,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -496,16 +496,16 @@
     <t>The identifier assigned by the lab when accessioning specimen(s). This is not necessarily the same as the specimen identifier, depending on local lab procedures.</t>
   </si>
   <si>
+    <t>1702: source value from SURGICAL PATHOLOGY - SURGICAL PATH ACC # (#63.08-.06)</t>
+  </si>
+  <si>
+    <t>Pathology.SurgicalPathology.SurgicalPathologyShortAccessionNumber</t>
+  </si>
+  <si>
     <t>.participation[typeCode=SBJ].act[classCode=ACSN, moodCode=EVN].id</t>
   </si>
   <si>
     <t>SPM-30 (v2.7+)</t>
-  </si>
-  <si>
-    <t>1702: source value from SURGICAL PATHOLOGY - SURGICAL PATH ACC # (#63.08-.06)</t>
-  </si>
-  <si>
-    <t>Pathology.SurgicalPathology.SurgicalPathologyShortAccessionNumber</t>
   </si>
   <si>
     <t>Specimen.status</t>
@@ -656,16 +656,16 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>1703: source value from SURGICAL PATHOLOGY - SPECIMEN &gt; SPECIMEN - SPECIMEN (#63.08-.012 &gt; 63.812-.01)</t>
+  </si>
+  <si>
+    <t>Pathology.SurgPathSpecimen.Specimen</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>1703: source value from SURGICAL PATHOLOGY - SPECIMEN &gt; SPECIMEN - SPECIMEN (#63.08-.012 &gt; 63.812-.01)</t>
-  </si>
-  <si>
-    <t>Pathology.SurgPathSpecimen.Specimen</t>
   </si>
   <si>
     <t>Specimen.subject</t>
@@ -1536,11 +1536,11 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="99.94921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="54.51171875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="105.95703125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="65.71484375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="105.95703125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="65.71484375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="99.94921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="54.51171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1768,13 +1768,13 @@
         <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>78</v>
@@ -2351,13 +2351,13 @@
         <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>78</v>
@@ -2468,13 +2468,13 @@
         <v>78</v>
       </c>
       <c r="AK8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>78</v>
@@ -2585,13 +2585,13 @@
         <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM9" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>78</v>
@@ -2704,13 +2704,13 @@
         <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM10" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>78</v>
@@ -2819,19 +2819,19 @@
         <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -2937,13 +2937,13 @@
         <v>154</v>
       </c>
       <c r="AL12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>157</v>
@@ -3051,19 +3051,19 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="14" hidden="true">
@@ -3168,19 +3168,19 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -3283,13 +3283,13 @@
         <v>78</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3400,13 +3400,13 @@
         <v>138</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3519,19 +3519,19 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -3641,13 +3641,13 @@
         <v>206</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>209</v>
@@ -3755,16 +3755,16 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>78</v>
@@ -3870,19 +3870,19 @@
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -3987,13 +3987,13 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -4104,19 +4104,19 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4219,19 +4219,19 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -4334,13 +4334,13 @@
         <v>78</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4451,13 +4451,13 @@
         <v>138</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -4570,13 +4570,13 @@
         <v>138</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -4685,19 +4685,19 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -4800,19 +4800,19 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -4918,13 +4918,13 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>78</v>
@@ -5030,19 +5030,19 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5145,19 +5145,19 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5262,19 +5262,19 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -5387,13 +5387,13 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -5496,13 +5496,13 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5611,13 +5611,13 @@
         <v>78</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5728,13 +5728,13 @@
         <v>138</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5847,13 +5847,13 @@
         <v>138</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5962,13 +5962,13 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6077,13 +6077,13 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6192,19 +6192,19 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -6307,13 +6307,13 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -6422,13 +6422,13 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -6537,13 +6537,13 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -6654,13 +6654,13 @@
         <v>138</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -6773,13 +6773,13 @@
         <v>138</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -6888,19 +6888,19 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="AL46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -7003,13 +7003,13 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7118,19 +7118,19 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -7233,19 +7233,19 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -7348,19 +7348,19 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -7463,19 +7463,19 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -7588,13 +7588,13 @@
         <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -7697,19 +7697,19 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file SURGICAL PATHOLOGY (#63.08) to Specimen</t>
+    <t>This StructureDefinition contains the maps for VistA file SURGICAL PATHOLOGY (63.08) to Specimen</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -496,7 +496,7 @@
     <t>The identifier assigned by the lab when accessioning specimen(s). This is not necessarily the same as the specimen identifier, depending on local lab procedures.</t>
   </si>
   <si>
-    <t>1702: source value from SURGICAL PATHOLOGY - SURGICAL PATH ACC # (#63.08-.06)</t>
+    <t>1702: source value from SURGICAL PATHOLOGY - SURGICAL PATH ACC # (63.08-.06)</t>
   </si>
   <si>
     <t>Pathology.SurgicalPathology.SurgicalPathologyShortAccessionNumber</t>
@@ -656,7 +656,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1703: source value from SURGICAL PATHOLOGY - SPECIMEN &gt; SPECIMEN - SPECIMEN (#63.08-.012 &gt; 63.812-.01)</t>
+    <t>1703: source value from SURGICAL PATHOLOGY - SPECIMEN &gt; SPECIMEN - SPECIMEN (63.08-.012 &gt; 63.812-.01)</t>
   </si>
   <si>
     <t>Pathology.SurgPathSpecimen.Specimen</t>
@@ -1536,7 +1536,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="105.95703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="104.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="65.71484375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="99.94921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsSurgicalPathologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
